--- a/Milestone 3/ProductBacklog.xlsx
+++ b/Milestone 3/ProductBacklog.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\guiba\Desktop\LDS\Entregue milestone 2\G14_8220849_8220238_8200066_8230153\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Utilizador\OneDrive\Documentos\GitHub\LDS\Milestone 3\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77D3E648-813D-45B3-932A-0718FB676542}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8726DDD4-E82E-49BA-8389-D755C47C736A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{982013A5-BAA1-47D2-B87C-A47FCA2ABBE8}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="11520" windowHeight="12960" xr2:uid="{982013A5-BAA1-47D2-B87C-A47FCA2ABBE8}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="116">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="117">
   <si>
     <t>Descrição</t>
   </si>
@@ -200,10 +200,6 @@
 - Frontend: Criar formulário de login. Guardar o token JWT de forma segura e enviá-lo nos cabeçalhos das requisições subsequentes.</t>
   </si>
   <si>
-    <t>- Backend: Criar endpoint POST /api/pacientes/registo. Validar dados de entrada (formato de email, complexidade da password). Hashing da password antes de guardar. 
-- Frontend: Criar formulário de registo com validação em tempo real.</t>
-  </si>
-  <si>
     <t>- Dado que um utilizador está autenticado, quando ele clica no botão de logout, o seu token de acesso é invalidado e ele é redirecionado para a página de login. 
 - Dado que um utilizador fez logout, quando ele tenta aceder a uma página protegida usando o token antigo, então o acesso é negado.</t>
   </si>
@@ -216,10 +212,6 @@
 - Dado que o Admin tenta criar um médico com um email que já existe, o sistema apresenta uma mensagem de erro.</t>
   </si>
   <si>
-    <t>- Backend: Criar endpoint POST /api/admin/medicos (protegido, só para Admins). 
-- Frontend-Web: Criar formulário na área de administração para adicionar médicos.</t>
-  </si>
-  <si>
     <t>- Dado que um utilizador autenticado está na sua página de perfil, quando ele edita os seus dados e guarda, a informação é atualizada na base de dados.</t>
   </si>
   <si>
@@ -274,10 +266,6 @@
     <t>- Dado que o Admin está a gerir a agenda de um Médico e existe um slot no estado "Livre", Quando ele o edita ou remove, o sistema atualiza o calendário desse Médico. O sistema deve impedir a edição ou remoção de um slot que já esteja no estado "Reservado". Se uma alteração num slot "Livre" afetar uma consulta "Pendente", o paciente deve ser notificado.</t>
   </si>
   <si>
-    <t>- Backend: Criar endpoints PUT /api/admin/medicos/{medicoId}/slots/{slotId} e DELETE /api/admin/medicos/{medicoId}/slots/{slotId}. A lógica de negócio deve verificar o estado do slot antes de permitir a operação. 
-- Frontend-Web: Na agenda do médico (dentro do painel de administração), permitir ao Admin clicar num slot livre para o editar ou remover.</t>
-  </si>
-  <si>
     <t>- Dado que o Paciente vê um horário livre na agenda de um médico, quando ele seleciona e confirma, a consulta é criada com o estado "Pendente de Confirmação". O slot de horário selecionado deve mudar o seu estado para "Reservado".</t>
   </si>
   <si>
@@ -298,15 +286,7 @@
     <t>- Dado que o Paciente acede ao seu dashboard, quando a página carrega, é exibida uma lista das suas consultas, ordenadas pela mais recente. O paciente pode inspecionar os detalhes de uma consulta.</t>
   </si>
   <si>
-    <t>- Backend: Criar endpoint GET /api/pacientes/me/consultas. 
-- Frontend: Apresentar os dados de forma clara, com paginação se necessário.</t>
-  </si>
-  <si>
     <t>- Dado que o Médico acede ao seu dashboard, quando a página carrega, é exibida a sua agenda com todas as consultas confirmadas. A agenda deve ser atualizada automaticamente quando novas consultas são marcadas ou canceladas.</t>
-  </si>
-  <si>
-    <t>- Backend: Criar endpoint GET /api/medicos/me/agenda. 
-- Frontend-Web: Criar a interface de agenda/calendário do médico.</t>
   </si>
   <si>
     <t>- Dado que o Admin está no seu painel, quando ele acede à gestão de médicos, ele pode criar, visualizar, editar e apagar perfis de médicos. O sistema deve validar os dados (ex: nº utente/ nif).</t>
@@ -317,10 +297,6 @@
   </si>
   <si>
     <t>- Dado que o Admin está na página de relatórios, quando ele seleciona um intervalo de datas, o sistema exibe um gráfico com o total de consultas por médico nesse período.</t>
-  </si>
-  <si>
-    <t>- Backend: Criar endpoint GET /api/admin/relatorios/consultas-por-medico. 
-- Frontend-Web: Criar a interface com filtros e uma biblioteca de gráficos.</t>
   </si>
   <si>
     <t>- Dado que o Admin está na página de relatórios, quando ele gera o relatório, o sistema exibe a percentagem de não comparências, podendo ser filtrada por médico ou período.</t>
@@ -389,10 +365,6 @@
     <t>US24: Notificação de Atraso do Médico</t>
   </si>
   <si>
-    <t>- Backend: Criar endpoint POST /api/consultas/{id}/atraso-medico que identifica o turno e envia notificações push aos pacientes seguintes. 
-- Frontend: Botão “Chegarei atrasado” disponível apenas antes da hora marcada.</t>
-  </si>
-  <si>
     <t>US25: Notificação de Atraso do Paciente</t>
   </si>
   <si>
@@ -404,29 +376,60 @@
 - Dado que já foi enviada uma notificação para a mesma consulta, o sistema não envia duplicadas.</t>
   </si>
   <si>
-    <t>- Backend: Criar endpoint POST /api/consultas/{id}/atraso-paciente que verifica o turno e envia notificações push ao médico e aos pacientes seguintes. 
+    <t>André</t>
+  </si>
+  <si>
+    <t>Diogo</t>
+  </si>
+  <si>
+    <t>Gonçalo</t>
+  </si>
+  <si>
+    <t>Guilherme</t>
+  </si>
+  <si>
+    <t>Alta</t>
+  </si>
+  <si>
+    <t>Essencial</t>
+  </si>
+  <si>
+    <t>Média</t>
+  </si>
+  <si>
+    <t>- Backend: Criar endpoint POST /api/pacientes. Validar dados de entrada (formato de email, complexidade da password). Hashing da password antes de guardar. 
+- Frontend: Criar formulário de registo com validação em tempo real.</t>
+  </si>
+  <si>
+    <t>- Backend: Criar endpoint POST /api/medicos (protegido, só para Admins). 
+- Frontend-Web: Criar formulário na área de administração para adicionar médicos.</t>
+  </si>
+  <si>
+    <t>- Backend: Criar endpoints PUT /api/admin/medicos/{medicoId}/horario e DELETE /api/admin/medicos/{medicoId}/horario/{horarioId}. A lógica de negócio deve verificar o estado do slot antes de permitir a operação. 
+- Frontend-Web: Na agenda do médico (dentro do painel de administração), permitir ao Admin clicar num slot livre para o editar ou remover.</t>
+  </si>
+  <si>
+    <t>- Backend: Criar endpoint GET /api/Dashboard/paciente/{pacienteId}/consultas. 
+- Frontend: Apresentar os dados de forma clara, com paginação se necessário.</t>
+  </si>
+  <si>
+    <t>- Backend: Criar endpoint GET /api/dashboard/medico/{medicoId}/consultas. 
+- Frontend-Web: Criar a interface de agenda/calendário do médico.</t>
+  </si>
+  <si>
+    <t>- Backend: Criar endpoint POST /api/notificacoes que verifica o turno e envia notificações push ao médico e aos pacientes seguintes. 
 - Frontend: Adicionar botão “Chegarei atrasado” visível até à hora da consulta.</t>
   </si>
   <si>
-    <t>André</t>
-  </si>
-  <si>
-    <t>Diogo</t>
-  </si>
-  <si>
-    <t>Gonçalo</t>
-  </si>
-  <si>
-    <t>Guilherme</t>
-  </si>
-  <si>
-    <t>Alta</t>
-  </si>
-  <si>
-    <t>Essencial</t>
-  </si>
-  <si>
-    <t>Média</t>
+    <t>- Backend: Criar endpoint POST /api/notificacoes que identifica o turno e envia notificações push aos pacientes seguintes. 
+- Frontend: Botão “Chegarei atrasado” disponível apenas antes da hora marcada.</t>
+  </si>
+  <si>
+    <t>- Backend: Criar endpoint GET /api/relatorios/consultas-por-medico. 
+- Frontend-Web: Criar a interface com filtros e uma biblioteca de gráficos.</t>
+  </si>
+  <si>
+    <t>Concluido</t>
   </si>
 </sst>
 </file>
@@ -622,11 +625,37 @@
       </border>
     </dxf>
     <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right style="thin">
+          <color theme="0"/>
+        </right>
+        <top style="thin">
+          <color theme="0"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border outline="0">
         <left style="thin">
           <color theme="0"/>
         </left>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color theme="0"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color theme="0"/>
+        </top>
+        <bottom/>
       </border>
     </dxf>
     <dxf>
@@ -638,32 +667,6 @@
         <right style="thin">
           <color theme="0"/>
         </right>
-        <top style="thin">
-          <color theme="0"/>
-        </top>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left/>
-        <right style="thin">
-          <color theme="0"/>
-        </right>
-        <top style="thin">
-          <color theme="0"/>
-        </top>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color theme="0"/>
-        </left>
-        <right/>
         <top style="thin">
           <color theme="0"/>
         </top>
@@ -784,18 +787,18 @@
     <tableColumn id="1" xr3:uid="{920B1D59-6FD0-416D-9FF2-FEE9D0983694}" name="Título" dataDxfId="7"/>
     <tableColumn id="2" xr3:uid="{680D0AC6-4CE8-48EF-BCFB-03948140A6E2}" name="Descrição" dataDxfId="6"/>
     <tableColumn id="3" xr3:uid="{1647D1E5-9627-4862-9C3D-8691065746F2}" name="Critérios de Aceitação" dataDxfId="5"/>
-    <tableColumn id="8" xr3:uid="{4490F14B-200A-4E29-8874-01BE4153AF22}" name="Notas/Tarefas Técnicas" dataDxfId="2"/>
-    <tableColumn id="4" xr3:uid="{B4C3319D-1302-4ECA-AEFD-266A6692D8C3}" name="Prioridade" dataDxfId="0"/>
-    <tableColumn id="5" xr3:uid="{666559DA-E2DD-419E-8EBC-4F1F0933AB1E}" name="Story Points" dataDxfId="1"/>
-    <tableColumn id="6" xr3:uid="{E81AB74D-11A4-4854-A3CF-BD62490C1E4E}" name="Responsável" dataDxfId="3"/>
-    <tableColumn id="7" xr3:uid="{FC635F6F-64ED-4D11-942C-0774FC7A12AD}" name="Estado" dataDxfId="4"/>
+    <tableColumn id="8" xr3:uid="{4490F14B-200A-4E29-8874-01BE4153AF22}" name="Notas/Tarefas Técnicas" dataDxfId="4"/>
+    <tableColumn id="4" xr3:uid="{B4C3319D-1302-4ECA-AEFD-266A6692D8C3}" name="Prioridade" dataDxfId="3"/>
+    <tableColumn id="5" xr3:uid="{666559DA-E2DD-419E-8EBC-4F1F0933AB1E}" name="Story Points" dataDxfId="2"/>
+    <tableColumn id="6" xr3:uid="{E81AB74D-11A4-4854-A3CF-BD62490C1E4E}" name="Responsável" dataDxfId="1"/>
+    <tableColumn id="7" xr3:uid="{FC635F6F-64ED-4D11-942C-0774FC7A12AD}" name="Estado" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema do Office">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -1112,22 +1115,22 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3AE6CC1C-EFAF-48DF-83E5-D6572C671D8C}">
   <dimension ref="B2:I28"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.15625" defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="1" max="1" width="7.42578125" style="1" customWidth="1"/>
-    <col min="2" max="2" width="32.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="29.85546875" style="1" customWidth="1"/>
-    <col min="4" max="4" width="71.140625" style="1" customWidth="1"/>
+    <col min="1" max="1" width="7.41796875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="32.83984375" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="29.83984375" style="1" customWidth="1"/>
+    <col min="4" max="4" width="71.15625" style="1" customWidth="1"/>
     <col min="5" max="5" width="49" style="1" customWidth="1"/>
-    <col min="6" max="6" width="12.42578125" style="1" customWidth="1"/>
+    <col min="6" max="6" width="12.41796875" style="1" customWidth="1"/>
     <col min="7" max="7" width="14" style="1" customWidth="1"/>
-    <col min="8" max="8" width="14.7109375" style="1" customWidth="1"/>
-    <col min="9" max="9" width="9.28515625" style="1" customWidth="1"/>
-    <col min="10" max="16384" width="9.140625" style="1"/>
+    <col min="8" max="8" width="14.68359375" style="1" customWidth="1"/>
+    <col min="9" max="9" width="9.26171875" style="1" customWidth="1"/>
+    <col min="10" max="16384" width="9.15625" style="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:9" ht="33" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="3" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:9" ht="33" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
+    <row r="3" spans="2:9" x14ac:dyDescent="0.55000000000000004">
       <c r="B3" s="2" t="s">
         <v>7</v>
       </c>
@@ -1153,7 +1156,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="2:9" ht="90" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:9" ht="72" x14ac:dyDescent="0.55000000000000004">
       <c r="B4" s="6" t="s">
         <v>8</v>
       </c>
@@ -1164,22 +1167,22 @@
         <v>10</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>53</v>
+        <v>108</v>
       </c>
       <c r="F4" s="11" t="s">
-        <v>114</v>
+        <v>106</v>
       </c>
       <c r="G4" s="13">
         <v>3</v>
       </c>
       <c r="H4" s="11" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="I4" s="10" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="5" spans="2:9" ht="90" x14ac:dyDescent="0.25">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="5" spans="2:9" ht="86.4" x14ac:dyDescent="0.55000000000000004">
       <c r="B5" s="6" t="s">
         <v>12</v>
       </c>
@@ -1193,19 +1196,19 @@
         <v>52</v>
       </c>
       <c r="F5" s="11" t="s">
-        <v>114</v>
+        <v>106</v>
       </c>
       <c r="G5" s="13">
         <v>3</v>
       </c>
       <c r="H5" s="12" t="s">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="I5" s="10" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="6" spans="2:9" ht="75" x14ac:dyDescent="0.25">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="6" spans="2:9" ht="57.6" x14ac:dyDescent="0.55000000000000004">
       <c r="B6" s="6" t="s">
         <v>14</v>
       </c>
@@ -1213,25 +1216,25 @@
         <v>15</v>
       </c>
       <c r="D6" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="E6" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="E6" s="9" t="s">
-        <v>55</v>
-      </c>
       <c r="F6" s="11" t="s">
-        <v>114</v>
+        <v>106</v>
       </c>
       <c r="G6" s="13">
         <v>3</v>
       </c>
       <c r="H6" s="12" t="s">
-        <v>111</v>
+        <v>103</v>
       </c>
       <c r="I6" s="10" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="7" spans="2:9" ht="75" x14ac:dyDescent="0.25">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="7" spans="2:9" ht="57.6" x14ac:dyDescent="0.55000000000000004">
       <c r="B7" s="6" t="s">
         <v>16</v>
       </c>
@@ -1239,25 +1242,25 @@
         <v>17</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E7" s="9" t="s">
-        <v>57</v>
+        <v>109</v>
       </c>
       <c r="F7" s="11" t="s">
-        <v>114</v>
+        <v>106</v>
       </c>
       <c r="G7" s="13">
         <v>8</v>
       </c>
       <c r="H7" s="12" t="s">
-        <v>112</v>
+        <v>104</v>
       </c>
       <c r="I7" s="10" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="8" spans="2:9" ht="105" x14ac:dyDescent="0.25">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="8" spans="2:9" ht="86.4" x14ac:dyDescent="0.55000000000000004">
       <c r="B8" s="6" t="s">
         <v>18</v>
       </c>
@@ -1265,25 +1268,25 @@
         <v>19</v>
       </c>
       <c r="D8" s="9" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="E8" s="9" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="F8" s="12" t="s">
-        <v>113</v>
+        <v>105</v>
       </c>
       <c r="G8" s="13">
         <v>1</v>
       </c>
       <c r="H8" s="12" t="s">
-        <v>111</v>
+        <v>103</v>
       </c>
       <c r="I8" s="10" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="9" spans="2:9" ht="90" x14ac:dyDescent="0.25">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="9" spans="2:9" ht="86.4" x14ac:dyDescent="0.55000000000000004">
       <c r="B9" s="6" t="s">
         <v>22</v>
       </c>
@@ -1291,25 +1294,25 @@
         <v>20</v>
       </c>
       <c r="D9" s="9" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E9" s="9" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="F9" s="11" t="s">
-        <v>114</v>
+        <v>106</v>
       </c>
       <c r="G9" s="13">
         <v>3</v>
       </c>
       <c r="H9" s="12" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="I9" s="10" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="10" spans="2:9" ht="90" x14ac:dyDescent="0.25">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="10" spans="2:9" ht="72" x14ac:dyDescent="0.55000000000000004">
       <c r="B10" s="6" t="s">
         <v>21</v>
       </c>
@@ -1317,25 +1320,25 @@
         <v>23</v>
       </c>
       <c r="D10" s="9" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="E10" s="9" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="F10" s="11" t="s">
-        <v>114</v>
+        <v>106</v>
       </c>
       <c r="G10" s="13">
         <v>5</v>
       </c>
       <c r="H10" s="12" t="s">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="I10" s="10" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="11" spans="2:9" ht="90" x14ac:dyDescent="0.25">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="11" spans="2:9" ht="72" x14ac:dyDescent="0.55000000000000004">
       <c r="B11" s="6" t="s">
         <v>24</v>
       </c>
@@ -1343,25 +1346,25 @@
         <v>25</v>
       </c>
       <c r="D11" s="9" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="E11" s="9" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="F11" s="11" t="s">
-        <v>114</v>
+        <v>106</v>
       </c>
       <c r="G11" s="13">
         <v>3</v>
       </c>
       <c r="H11" s="12" t="s">
-        <v>112</v>
+        <v>104</v>
       </c>
       <c r="I11" s="10" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="12" spans="2:9" ht="90" x14ac:dyDescent="0.25">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="12" spans="2:9" ht="72" x14ac:dyDescent="0.55000000000000004">
       <c r="B12" s="6" t="s">
         <v>26</v>
       </c>
@@ -1369,25 +1372,25 @@
         <v>27</v>
       </c>
       <c r="D12" s="9" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="E12" s="9" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="F12" s="11" t="s">
-        <v>114</v>
+        <v>106</v>
       </c>
       <c r="G12" s="13">
         <v>3</v>
       </c>
       <c r="H12" s="12" t="s">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="I12" s="10" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="13" spans="2:9" ht="120" x14ac:dyDescent="0.25">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="13" spans="2:9" ht="100.8" x14ac:dyDescent="0.55000000000000004">
       <c r="B13" s="6" t="s">
         <v>28</v>
       </c>
@@ -1395,25 +1398,25 @@
         <v>29</v>
       </c>
       <c r="D13" s="9" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E13" s="9" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="F13" s="11" t="s">
-        <v>114</v>
+        <v>106</v>
       </c>
       <c r="G13" s="13">
         <v>5</v>
       </c>
       <c r="H13" s="12" t="s">
-        <v>111</v>
+        <v>103</v>
       </c>
       <c r="I13" s="10" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="14" spans="2:9" ht="135" x14ac:dyDescent="0.25">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="14" spans="2:9" ht="100.8" x14ac:dyDescent="0.55000000000000004">
       <c r="B14" s="6" t="s">
         <v>30</v>
       </c>
@@ -1421,25 +1424,25 @@
         <v>31</v>
       </c>
       <c r="D14" s="9" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E14" s="9" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="F14" s="11" t="s">
-        <v>114</v>
+        <v>106</v>
       </c>
       <c r="G14" s="13">
         <v>5</v>
       </c>
       <c r="H14" s="12" t="s">
-        <v>112</v>
+        <v>104</v>
       </c>
       <c r="I14" s="10" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="15" spans="2:9" ht="135" x14ac:dyDescent="0.25">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="15" spans="2:9" ht="115.2" x14ac:dyDescent="0.55000000000000004">
       <c r="B15" s="6" t="s">
         <v>32</v>
       </c>
@@ -1447,25 +1450,25 @@
         <v>33</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>73</v>
+        <v>110</v>
       </c>
       <c r="F15" s="11" t="s">
-        <v>114</v>
+        <v>106</v>
       </c>
       <c r="G15" s="13">
         <v>5</v>
       </c>
       <c r="H15" s="11" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="I15" s="10" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="16" spans="2:9" ht="75" x14ac:dyDescent="0.25">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="16" spans="2:9" ht="57.6" x14ac:dyDescent="0.55000000000000004">
       <c r="B16" s="6" t="s">
         <v>34</v>
       </c>
@@ -1473,25 +1476,25 @@
         <v>35</v>
       </c>
       <c r="D16" s="9" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="E16" s="9" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="F16" s="11" t="s">
-        <v>114</v>
+        <v>106</v>
       </c>
       <c r="G16" s="13">
         <v>8</v>
       </c>
       <c r="H16" s="12" t="s">
-        <v>111</v>
+        <v>103</v>
       </c>
       <c r="I16" s="10" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="17" spans="2:9" ht="90" x14ac:dyDescent="0.25">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="17" spans="2:9" ht="86.4" x14ac:dyDescent="0.55000000000000004">
       <c r="B17" s="6" t="s">
         <v>36</v>
       </c>
@@ -1499,51 +1502,51 @@
         <v>37</v>
       </c>
       <c r="D17" s="9" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="E17" s="9" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="F17" s="11" t="s">
-        <v>114</v>
+        <v>106</v>
       </c>
       <c r="G17" s="13">
         <v>5</v>
       </c>
       <c r="H17" s="12" t="s">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="I17" s="10" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="18" spans="2:9" ht="195" x14ac:dyDescent="0.25">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="18" spans="2:9" ht="129.6" x14ac:dyDescent="0.55000000000000004">
       <c r="B18" s="6" t="s">
         <v>38</v>
       </c>
       <c r="C18" s="8" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="D18" s="9" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="E18" s="9" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="F18" s="12" t="s">
-        <v>113</v>
+        <v>105</v>
       </c>
       <c r="G18" s="13">
         <v>5</v>
       </c>
       <c r="H18" s="12" t="s">
-        <v>112</v>
+        <v>104</v>
       </c>
       <c r="I18" s="10" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="19" spans="2:9" ht="75" x14ac:dyDescent="0.25">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="19" spans="2:9" ht="72" x14ac:dyDescent="0.55000000000000004">
       <c r="B19" s="6" t="s">
         <v>39</v>
       </c>
@@ -1551,51 +1554,51 @@
         <v>40</v>
       </c>
       <c r="D19" s="9" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="E19" s="9" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="F19" s="12" t="s">
-        <v>115</v>
+        <v>107</v>
       </c>
       <c r="G19" s="13">
         <v>2</v>
       </c>
       <c r="H19" s="12" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="I19" s="10" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="20" spans="2:9" ht="90" x14ac:dyDescent="0.25">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="20" spans="2:9" ht="72" x14ac:dyDescent="0.55000000000000004">
       <c r="B20" s="6" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="C20" s="8" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="D20" s="9" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="E20" s="9" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="F20" s="12" t="s">
-        <v>113</v>
+        <v>105</v>
       </c>
       <c r="G20" s="13">
         <v>2</v>
       </c>
       <c r="H20" s="12" t="s">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="I20" s="10" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="21" spans="2:9" ht="60" x14ac:dyDescent="0.25">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="21" spans="2:9" ht="57.6" x14ac:dyDescent="0.55000000000000004">
       <c r="B21" s="6" t="s">
         <v>45</v>
       </c>
@@ -1603,25 +1606,25 @@
         <v>41</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>80</v>
+        <v>111</v>
       </c>
       <c r="F21" s="11" t="s">
-        <v>113</v>
+        <v>105</v>
       </c>
       <c r="G21" s="13">
         <v>5</v>
       </c>
       <c r="H21" s="11" t="s">
-        <v>111</v>
+        <v>103</v>
       </c>
       <c r="I21" s="10" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="22" spans="2:9" ht="75" x14ac:dyDescent="0.25">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="22" spans="2:9" ht="57.6" x14ac:dyDescent="0.55000000000000004">
       <c r="B22" s="6" t="s">
         <v>42</v>
       </c>
@@ -1629,25 +1632,25 @@
         <v>43</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="E22" s="9" t="s">
-        <v>82</v>
+        <v>112</v>
       </c>
       <c r="F22" s="12" t="s">
-        <v>114</v>
+        <v>106</v>
       </c>
       <c r="G22" s="13">
         <v>8</v>
       </c>
       <c r="H22" s="12" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="I22" s="10" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="23" spans="2:9" ht="75" x14ac:dyDescent="0.25">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="23" spans="2:9" ht="57.6" x14ac:dyDescent="0.55000000000000004">
       <c r="B23" s="6" t="s">
         <v>48</v>
       </c>
@@ -1655,25 +1658,25 @@
         <v>44</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="E23" s="9" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="F23" s="12" t="s">
-        <v>114</v>
+        <v>106</v>
       </c>
       <c r="G23" s="13">
         <v>8</v>
       </c>
       <c r="H23" s="12" t="s">
-        <v>112</v>
+        <v>104</v>
       </c>
       <c r="I23" s="10" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="24" spans="2:9" ht="90" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:9" ht="72" x14ac:dyDescent="0.55000000000000004">
       <c r="B24" s="6" t="s">
         <v>49</v>
       </c>
@@ -1681,25 +1684,25 @@
         <v>46</v>
       </c>
       <c r="D24" s="5" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="E24" s="5" t="s">
-        <v>86</v>
+        <v>115</v>
       </c>
       <c r="F24" s="11" t="s">
-        <v>113</v>
+        <v>105</v>
       </c>
       <c r="G24" s="13">
         <v>2</v>
       </c>
       <c r="H24" s="11" t="s">
-        <v>112</v>
+        <v>104</v>
       </c>
       <c r="I24" s="10" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="25" spans="2:9" ht="90" x14ac:dyDescent="0.25">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="25" spans="2:9" ht="72" x14ac:dyDescent="0.55000000000000004">
       <c r="B25" s="6" t="s">
         <v>50</v>
       </c>
@@ -1707,100 +1710,100 @@
         <v>47</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="E25" s="5" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="F25" s="11" t="s">
-        <v>115</v>
+        <v>107</v>
       </c>
       <c r="G25" s="13">
         <v>2</v>
       </c>
       <c r="H25" s="11" t="s">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="I25" s="10" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="26" spans="2:9" ht="150" x14ac:dyDescent="0.25">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="26" spans="2:9" ht="129.6" x14ac:dyDescent="0.55000000000000004">
       <c r="B26" s="6" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="C26" s="7" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="D26" s="5" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="E26" s="5" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="F26" s="12" t="s">
-        <v>114</v>
+        <v>106</v>
       </c>
       <c r="G26" s="13">
         <v>5</v>
       </c>
       <c r="H26" s="11" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="I26" s="10" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="27" spans="2:9" ht="105" x14ac:dyDescent="0.25">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="27" spans="2:9" ht="100.8" x14ac:dyDescent="0.55000000000000004">
       <c r="B27" s="6" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="C27" s="7" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="D27" s="5" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="E27" s="5" t="s">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="F27" s="12" t="s">
-        <v>113</v>
+        <v>105</v>
       </c>
       <c r="G27" s="13">
         <v>5</v>
       </c>
       <c r="H27" s="11" t="s">
-        <v>111</v>
+        <v>103</v>
       </c>
       <c r="I27" s="10" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="28" spans="2:9" ht="120" x14ac:dyDescent="0.25">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="28" spans="2:9" ht="86.4" x14ac:dyDescent="0.55000000000000004">
       <c r="B28" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="C28" s="7" t="s">
+        <v>99</v>
+      </c>
+      <c r="D28" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="E28" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="F28" s="12" t="s">
         <v>105</v>
-      </c>
-      <c r="C28" s="7" t="s">
-        <v>106</v>
-      </c>
-      <c r="D28" s="5" t="s">
-        <v>107</v>
-      </c>
-      <c r="E28" s="5" t="s">
-        <v>108</v>
-      </c>
-      <c r="F28" s="12" t="s">
-        <v>113</v>
       </c>
       <c r="G28" s="13">
         <v>5</v>
       </c>
       <c r="H28" s="11" t="s">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="I28" s="10" t="s">
-        <v>11</v>
+        <v>116</v>
       </c>
     </row>
   </sheetData>
